--- a/research/traditional_assets/database/data/portugal/portugal_entertainment.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_entertainment.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07855000000000001</v>
+        <v>0.08645</v>
+      </c>
+      <c r="E2">
+        <v>0.0229</v>
       </c>
       <c r="G2">
-        <v>-0.3827373612823674</v>
+        <v>-0.280500742626777</v>
       </c>
       <c r="H2">
-        <v>-0.3827373612823674</v>
+        <v>-0.280500742626777</v>
       </c>
       <c r="I2">
-        <v>-0.5240443896424167</v>
+        <v>-0.3183221823595256</v>
       </c>
       <c r="J2">
-        <v>-0.5195156109664946</v>
+        <v>-0.3131590282355031</v>
       </c>
       <c r="K2">
-        <v>5.11</v>
+        <v>-12.73</v>
       </c>
       <c r="L2">
-        <v>0.01260172626387176</v>
+        <v>-0.027010396774878</v>
       </c>
       <c r="M2">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0002603928734582001</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.0111545988258317</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0002603928734582001</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.0111545988258317</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>64.88</v>
+        <v>51.83</v>
       </c>
       <c r="V2">
-        <v>0.2963910461397899</v>
+        <v>0.2594094094094094</v>
       </c>
       <c r="W2">
-        <v>-0.1408927449020598</v>
+        <v>-0.03466696505813623</v>
       </c>
       <c r="X2">
-        <v>0.1755948566914614</v>
+        <v>0.3430596586130263</v>
       </c>
       <c r="Y2">
-        <v>-0.3164876015935212</v>
+        <v>-0.3777266236711625</v>
       </c>
       <c r="Z2">
-        <v>0.8739224137931035</v>
+        <v>0.8967300642934869</v>
       </c>
       <c r="AA2">
-        <v>-0.4641926359990581</v>
+        <v>-0.321339907465697</v>
       </c>
       <c r="AB2">
-        <v>0.08290073892045483</v>
+        <v>0.1416699858408829</v>
       </c>
       <c r="AC2">
-        <v>-0.550277486281344</v>
+        <v>-0.4645622345091777</v>
       </c>
       <c r="AD2">
-        <v>690.1</v>
+        <v>666</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.1662227302220781</v>
       </c>
       <c r="AF2">
-        <v>690.1</v>
+        <v>666.1662227302221</v>
       </c>
       <c r="AG2">
-        <v>625.22</v>
+        <v>614.3362227302221</v>
       </c>
       <c r="AH2">
-        <v>0.7591859185918592</v>
+        <v>0.7692750655215285</v>
       </c>
       <c r="AI2">
-        <v>0.9946670510233496</v>
+        <v>1.062862353731144</v>
       </c>
       <c r="AJ2">
-        <v>0.7406766810406104</v>
+        <v>0.7545865244394032</v>
       </c>
       <c r="AK2">
-        <v>0.9941168988106595</v>
+        <v>1.068529340198639</v>
       </c>
       <c r="AL2">
-        <v>57.78</v>
+        <v>51.12</v>
       </c>
       <c r="AM2">
-        <v>46.48</v>
+        <v>42.32700000000001</v>
       </c>
       <c r="AN2">
-        <v>-5.353762606671839</v>
+        <v>-9.60318375821894</v>
       </c>
       <c r="AO2">
-        <v>-3.677743163724472</v>
+        <v>-2.935054773082942</v>
       </c>
       <c r="AP2">
-        <v>-4.850426687354538</v>
+        <v>-8.858233688000663</v>
       </c>
       <c r="AQ2">
-        <v>-4.571858864027538</v>
+        <v>-3.544782290263897</v>
       </c>
     </row>
     <row r="3">
@@ -719,25 +719,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0191</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="G3">
-        <v>-0.3747412008281574</v>
+        <v>-0.2758089368258859</v>
       </c>
       <c r="H3">
-        <v>-0.3747412008281574</v>
+        <v>-0.2758089368258859</v>
       </c>
       <c r="I3">
-        <v>-0.39648033126294</v>
+        <v>-0.008012326656394453</v>
       </c>
       <c r="J3">
-        <v>-0.39648033126294</v>
+        <v>-0.008012326656394453</v>
       </c>
       <c r="K3">
-        <v>-11.6</v>
+        <v>-1.08</v>
       </c>
       <c r="L3">
-        <v>-0.1200828157349896</v>
+        <v>-0.008320493066255779</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,73 +761,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>21.6</v>
       </c>
       <c r="V3">
-        <v>0.03657817109144543</v>
+        <v>0.3829787234042554</v>
       </c>
       <c r="W3">
-        <v>0.703030303030303</v>
+        <v>0.02706766917293233</v>
       </c>
       <c r="X3">
-        <v>0.1971527389243338</v>
+        <v>0.3966572037292725</v>
       </c>
       <c r="Y3">
-        <v>0.5058775641059692</v>
+        <v>-0.3695895345563401</v>
       </c>
       <c r="Z3">
-        <v>0.689802913453299</v>
+        <v>1.160897951882658</v>
       </c>
       <c r="AA3">
-        <v>-0.2734932876321051</v>
+        <v>-0.009301493605223147</v>
       </c>
       <c r="AB3">
-        <v>0.08195549060295616</v>
+        <v>0.1417650623719683</v>
       </c>
       <c r="AC3">
-        <v>-0.3554487782350613</v>
+        <v>-0.1510665559771914</v>
       </c>
       <c r="AD3">
-        <v>154</v>
+        <v>179.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>154</v>
+        <v>179.9</v>
       </c>
       <c r="AG3">
-        <v>151.52</v>
+        <v>158.3</v>
       </c>
       <c r="AH3">
-        <v>0.6943192064923354</v>
+        <v>0.7613203554803216</v>
       </c>
       <c r="AI3">
-        <v>1.205951448707909</v>
+        <v>1.256284916201117</v>
       </c>
       <c r="AJ3">
-        <v>0.6908626664234908</v>
+        <v>0.7373078714485328</v>
       </c>
       <c r="AK3">
-        <v>1.210030346590002</v>
+        <v>1.301809210526316</v>
       </c>
       <c r="AL3">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="AM3">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="AN3">
-        <v>-15.55555555555556</v>
+        <v>6.662962962962963</v>
       </c>
       <c r="AO3">
-        <v>-3.245762711864406</v>
+        <v>-0.08455284552845528</v>
       </c>
       <c r="AP3">
-        <v>-15.30505050505051</v>
+        <v>5.862962962962963</v>
       </c>
       <c r="AQ3">
-        <v>-3.245762711864406</v>
+        <v>-0.08455284552845528</v>
       </c>
     </row>
     <row r="4">
@@ -847,25 +847,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.057</v>
+        <v>0.0572</v>
       </c>
       <c r="G4">
-        <v>-1.10762331838565</v>
+        <v>-0.4655367231638418</v>
       </c>
       <c r="H4">
-        <v>-1.10762331838565</v>
+        <v>-0.4655367231638418</v>
       </c>
       <c r="I4">
-        <v>-1.147085201793722</v>
+        <v>-0.4870056497175141</v>
       </c>
       <c r="J4">
-        <v>-1.147085201793722</v>
+        <v>-0.4870056497175141</v>
       </c>
       <c r="K4">
-        <v>-20.6</v>
+        <v>-36.6</v>
       </c>
       <c r="L4">
-        <v>-0.1847533632286996</v>
+        <v>-0.2067796610169492</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,73 +889,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>52.3</v>
+        <v>25.2</v>
       </c>
       <c r="V4">
-        <v>0.433665008291874</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="W4">
-        <v>-0.113561190738699</v>
+        <v>-0.2149148561362302</v>
       </c>
       <c r="X4">
-        <v>0.154036974458589</v>
+        <v>0.2894621134967801</v>
       </c>
       <c r="Y4">
-        <v>-0.2675981651972881</v>
+        <v>-0.5043769696330103</v>
       </c>
       <c r="Z4">
-        <v>0.3879475314011343</v>
+        <v>0.6084565142660707</v>
       </c>
       <c r="AA4">
-        <v>-0.4450088723426465</v>
+        <v>-0.2963217600550017</v>
       </c>
       <c r="AB4">
-        <v>0.0838459872379535</v>
+        <v>0.1415749093097975</v>
       </c>
       <c r="AC4">
-        <v>-0.5288548595806</v>
+        <v>-0.4378966693647993</v>
       </c>
       <c r="AD4">
-        <v>172.9</v>
+        <v>179.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>172.9</v>
+        <v>179.2</v>
       </c>
       <c r="AG4">
-        <v>120.6</v>
+        <v>154</v>
       </c>
       <c r="AH4">
-        <v>0.5890971039182283</v>
+        <v>0.6497461928934011</v>
       </c>
       <c r="AI4">
-        <v>0.5037878787878788</v>
+        <v>0.6111869031377899</v>
       </c>
       <c r="AJ4">
-        <v>0.5000000000000001</v>
+        <v>0.6145251396648045</v>
       </c>
       <c r="AK4">
-        <v>0.4145754554829838</v>
+        <v>0.5746268656716418</v>
       </c>
       <c r="AL4">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="AM4">
-        <v>9.44</v>
+        <v>9.65</v>
       </c>
       <c r="AN4">
-        <v>-1.4</v>
+        <v>-2.174757281553398</v>
       </c>
       <c r="AO4">
-        <v>-7.65868263473054</v>
+        <v>-6.481203007518797</v>
       </c>
       <c r="AP4">
-        <v>-0.9765182186234819</v>
+        <v>-1.868932038834951</v>
       </c>
       <c r="AQ4">
-        <v>-13.54872881355932</v>
+        <v>-8.932642487046632</v>
       </c>
     </row>
     <row r="5">
@@ -975,118 +975,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.152</v>
+        <v>0.0775</v>
       </c>
       <c r="G5">
-        <v>0.1213618890719385</v>
+        <v>-0.02767797737857618</v>
       </c>
       <c r="H5">
-        <v>0.1213618890719385</v>
+        <v>-0.02767797737857618</v>
       </c>
       <c r="I5">
-        <v>-0.100494233937397</v>
+        <v>-0.2927478376580173</v>
       </c>
       <c r="J5">
-        <v>-0.09702035918400553</v>
+        <v>-0.2827553781326236</v>
       </c>
       <c r="K5">
-        <v>39.6</v>
+        <v>21.7</v>
       </c>
       <c r="L5">
-        <v>0.2174629324546952</v>
+        <v>0.1443779108449767</v>
       </c>
       <c r="M5">
-        <v>0.057</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.002893401015228426</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.001439393939393939</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.057</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.002893401015228426</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.001439393939393939</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>10.1</v>
+        <v>5.03</v>
       </c>
       <c r="V5">
-        <v>0.5126903553299492</v>
+        <v>0.2372641509433963</v>
       </c>
       <c r="W5">
-        <v>-0.1682242990654206</v>
+        <v>-0.0964015992892048</v>
       </c>
       <c r="X5">
-        <v>1.029139709506844</v>
+        <v>1.303175220460981</v>
       </c>
       <c r="Y5">
-        <v>-1.197364008572264</v>
+        <v>-1.399576819750186</v>
       </c>
       <c r="Z5">
-        <v>4.982216142270864</v>
+        <v>1.224938875305624</v>
       </c>
       <c r="AA5">
-        <v>-0.4833763996554697</v>
+        <v>-0.3463580548763923</v>
       </c>
       <c r="AB5">
-        <v>0.08832371332661831</v>
+        <v>0.1448697447771639</v>
       </c>
       <c r="AC5">
-        <v>-0.571700112982088</v>
+        <v>-0.4912277996535562</v>
       </c>
       <c r="AD5">
-        <v>363.2</v>
+        <v>306.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>363.2</v>
+        <v>306.9</v>
       </c>
       <c r="AG5">
-        <v>353.1</v>
+        <v>301.87</v>
       </c>
       <c r="AH5">
-        <v>0.9485505353878297</v>
+        <v>0.9353855531850046</v>
       </c>
       <c r="AI5">
-        <v>1.629430237774787</v>
+        <v>1.613564668769716</v>
       </c>
       <c r="AJ5">
-        <v>0.9471566523605151</v>
+        <v>0.9343795462283716</v>
       </c>
       <c r="AK5">
-        <v>1.659304511278196</v>
+        <v>1.630231678997678</v>
       </c>
       <c r="AL5">
-        <v>28.2</v>
+        <v>24.5</v>
       </c>
       <c r="AM5">
-        <v>25.35</v>
+        <v>19.73</v>
       </c>
       <c r="AN5">
-        <v>16.43438914027149</v>
+        <v>-73.77403846153845</v>
       </c>
       <c r="AO5">
-        <v>-0.648936170212766</v>
+        <v>-1.795918367346939</v>
       </c>
       <c r="AP5">
-        <v>15.97737556561086</v>
+        <v>-72.56490384615384</v>
       </c>
       <c r="AQ5">
-        <v>-0.7218934911242605</v>
+        <v>-2.230106436898124</v>
       </c>
     </row>
     <row r="6">
@@ -1106,25 +1103,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.138</v>
+        <v>0.09910000000000001</v>
+      </c>
+      <c r="E6">
+        <v>0.0229</v>
       </c>
       <c r="G6">
-        <v>-1.150326797385621</v>
+        <v>-0.6929577464788733</v>
       </c>
       <c r="H6">
-        <v>-1.150326797385621</v>
+        <v>-0.6929577464788733</v>
       </c>
       <c r="I6">
-        <v>-1.830065359477124</v>
+        <v>-1.322904545496086</v>
       </c>
       <c r="J6">
-        <v>-1.830065359477124</v>
+        <v>-1.282230166933072</v>
       </c>
       <c r="K6">
-        <v>-2.29</v>
+        <v>3.25</v>
       </c>
       <c r="L6">
-        <v>-0.1496732026143791</v>
+        <v>0.2288732394366197</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1133,7 +1133,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1142,7 +1142,7 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1154,46 +1154,61 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>0.08024924363490883</v>
+        <v>0.1409890698513052</v>
+      </c>
+      <c r="Z6">
+        <v>85.42754640733195</v>
+      </c>
+      <c r="AA6">
+        <v>-109.537777090556</v>
       </c>
       <c r="AB6">
-        <v>0.08024924363490883</v>
+        <v>0.1404979241427579</v>
+      </c>
+      <c r="AC6">
+        <v>-109.6782750146988</v>
       </c>
       <c r="AD6">
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.1662227302220781</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.1662227302220781</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>0.1662227302220781</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.006451187353399296</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>0.006451187353399296</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
       </c>
       <c r="AL6">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AM6">
-        <v>-0.1099999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="AN6">
         <v>-0</v>
       </c>
       <c r="AO6">
-        <v>-25.92592592592592</v>
+        <v>-18.43137254901961</v>
       </c>
       <c r="AP6">
-        <v>-0</v>
+        <v>-0.01697536052104556</v>
       </c>
       <c r="AQ6">
-        <v>254.5454545454548</v>
+        <v>-29.05718701700155</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/portugal/portugal_entertainment.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_entertainment.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08645</v>
+        <v>0.0883</v>
       </c>
       <c r="E2">
-        <v>0.0229</v>
+        <v>-0.272</v>
       </c>
       <c r="G2">
-        <v>-0.280500742626777</v>
+        <v>-0.1626988803771361</v>
       </c>
       <c r="H2">
-        <v>-0.280500742626777</v>
+        <v>-0.1626988803771361</v>
       </c>
       <c r="I2">
-        <v>-0.3183221823595256</v>
+        <v>-0.3339226085248477</v>
       </c>
       <c r="J2">
-        <v>-0.3131590282355031</v>
+        <v>-0.3265990557152175</v>
       </c>
       <c r="K2">
-        <v>-12.73</v>
+        <v>54.8</v>
       </c>
       <c r="L2">
-        <v>-0.027010396774878</v>
+        <v>0.1076409349833039</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>51.83</v>
+        <v>56.32</v>
       </c>
       <c r="V2">
-        <v>0.2594094094094094</v>
+        <v>0.2115702479338843</v>
       </c>
       <c r="W2">
-        <v>-0.03466696505813623</v>
+        <v>-0.09969257795344752</v>
       </c>
       <c r="X2">
-        <v>0.3430596586130263</v>
+        <v>0.2325160560786009</v>
       </c>
       <c r="Y2">
-        <v>-0.3777266236711625</v>
+        <v>-0.3322086340320484</v>
       </c>
       <c r="Z2">
-        <v>0.8967300642934869</v>
+        <v>1.056180241483756</v>
       </c>
       <c r="AA2">
-        <v>-0.321339907465697</v>
+        <v>-0.3157751240782423</v>
       </c>
       <c r="AB2">
-        <v>0.1416699858408829</v>
+        <v>0.1002416463656472</v>
       </c>
       <c r="AC2">
-        <v>-0.4645622345091777</v>
+        <v>-0.4160167704438895</v>
       </c>
       <c r="AD2">
-        <v>666</v>
+        <v>614.2</v>
       </c>
       <c r="AE2">
-        <v>0.1662227302220781</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>666.1662227302221</v>
+        <v>614.2</v>
       </c>
       <c r="AG2">
-        <v>614.3362227302221</v>
+        <v>557.88</v>
       </c>
       <c r="AH2">
-        <v>0.7692750655215285</v>
+        <v>0.6976374375283961</v>
       </c>
       <c r="AI2">
-        <v>1.062862353731144</v>
+        <v>0.9952683432719731</v>
       </c>
       <c r="AJ2">
-        <v>0.7545865244394032</v>
+        <v>0.6769731094068537</v>
       </c>
       <c r="AK2">
-        <v>1.068529340198639</v>
+        <v>0.9947931526390871</v>
       </c>
       <c r="AL2">
-        <v>51.12</v>
+        <v>59.9</v>
       </c>
       <c r="AM2">
-        <v>42.32700000000001</v>
+        <v>50.76</v>
       </c>
       <c r="AN2">
-        <v>-9.60318375821894</v>
+        <v>-7.181945743685689</v>
       </c>
       <c r="AO2">
-        <v>-2.935054773082942</v>
+        <v>-2.838063439065109</v>
       </c>
       <c r="AP2">
-        <v>-8.858233688000663</v>
+        <v>-6.523386342376052</v>
       </c>
       <c r="AQ2">
-        <v>-3.544782290263897</v>
+        <v>-3.34909377462569</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sporting Clube de Portugal - Futebol, SAD (ENXTLS:SCP)</t>
+          <t>Sport Lisboa e Benfica - Futebol, SAD (ENXTLS:SLBEN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09539999999999998</v>
+        <v>0.1</v>
+      </c>
+      <c r="E3">
+        <v>-0.272</v>
       </c>
       <c r="G3">
-        <v>-0.2758089368258859</v>
+        <v>-0.3231992516370439</v>
       </c>
       <c r="H3">
-        <v>-0.2758089368258859</v>
+        <v>-0.3231992516370439</v>
       </c>
       <c r="I3">
-        <v>-0.008012326656394453</v>
+        <v>-0.3409728718428438</v>
       </c>
       <c r="J3">
-        <v>-0.008012326656394453</v>
+        <v>-0.3409728718428438</v>
       </c>
       <c r="K3">
-        <v>-1.08</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
-        <v>-0.008320493066255779</v>
+        <v>0.02151543498596819</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,79 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>21.6</v>
+        <v>31.2</v>
       </c>
       <c r="V3">
-        <v>0.3829787234042554</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="W3">
-        <v>0.02706766917293233</v>
+        <v>0.04035087719298245</v>
       </c>
       <c r="X3">
-        <v>0.3966572037292725</v>
+        <v>0.2325160560786009</v>
       </c>
       <c r="Y3">
-        <v>-0.3695895345563401</v>
+        <v>-0.1921651788856184</v>
       </c>
       <c r="Z3">
-        <v>1.160897951882658</v>
+        <v>0.7977611940298508</v>
       </c>
       <c r="AA3">
-        <v>-0.009301493605223147</v>
+        <v>-0.2720149253731344</v>
       </c>
       <c r="AB3">
-        <v>0.1417650623719683</v>
+        <v>0.09880716541618192</v>
       </c>
       <c r="AC3">
-        <v>-0.1510665559771914</v>
+        <v>-0.3708220907893163</v>
       </c>
       <c r="AD3">
-        <v>179.9</v>
+        <v>185</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>179.9</v>
+        <v>185</v>
       </c>
       <c r="AG3">
-        <v>158.3</v>
+        <v>153.8</v>
       </c>
       <c r="AH3">
-        <v>0.7613203554803216</v>
+        <v>0.7164988381099923</v>
       </c>
       <c r="AI3">
-        <v>1.256284916201117</v>
+        <v>0.5994815294880104</v>
       </c>
       <c r="AJ3">
-        <v>0.7373078714485328</v>
+        <v>0.6775330396475772</v>
       </c>
       <c r="AK3">
-        <v>1.301809210526316</v>
+        <v>0.5544340302811825</v>
       </c>
       <c r="AL3">
-        <v>12.3</v>
+        <v>17.9</v>
       </c>
       <c r="AM3">
-        <v>12.3</v>
+        <v>13.74</v>
       </c>
       <c r="AN3">
-        <v>6.662962962962963</v>
+        <v>-2.677279305354559</v>
       </c>
       <c r="AO3">
-        <v>-0.08455284552845528</v>
+        <v>-4.072625698324023</v>
       </c>
       <c r="AP3">
-        <v>5.862962962962963</v>
+        <v>-2.22575976845152</v>
       </c>
       <c r="AQ3">
-        <v>-0.08455284552845528</v>
+        <v>-5.305676855895197</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sport Lisboa e Benfica - Futebol, SAD (ENXTLS:SLBEN)</t>
+          <t>Sporting Clube de Portugal - Futebol, SAD (ENXTLS:SCP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,25 +850,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0572</v>
+        <v>0.0584</v>
       </c>
       <c r="G4">
-        <v>-0.4655367231638418</v>
+        <v>-0.07430124223602484</v>
       </c>
       <c r="H4">
-        <v>-0.4655367231638418</v>
+        <v>-0.07430124223602484</v>
       </c>
       <c r="I4">
-        <v>-0.4870056497175141</v>
+        <v>-0.3781055900621118</v>
       </c>
       <c r="J4">
-        <v>-0.4870056497175141</v>
+        <v>-0.3718938553682343</v>
       </c>
       <c r="K4">
-        <v>-36.6</v>
+        <v>27.5</v>
       </c>
       <c r="L4">
-        <v>-0.2067796610169492</v>
+        <v>0.2135093167701863</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,7 +877,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -883,79 +886,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>25.2</v>
+        <v>9.42</v>
       </c>
       <c r="V4">
-        <v>0.2608695652173913</v>
+        <v>0.05747406955460647</v>
       </c>
       <c r="W4">
-        <v>-0.2149148561362302</v>
+        <v>-1.617647058823529</v>
       </c>
       <c r="X4">
-        <v>0.2894621134967801</v>
+        <v>0.1534873923018874</v>
       </c>
       <c r="Y4">
-        <v>-0.5043769696330103</v>
+        <v>-1.771134451125417</v>
       </c>
       <c r="Z4">
-        <v>0.6084565142660707</v>
+        <v>0.84910013844024</v>
       </c>
       <c r="AA4">
-        <v>-0.2963217600550017</v>
+        <v>-0.3157751240782423</v>
       </c>
       <c r="AB4">
-        <v>0.1415749093097975</v>
+        <v>0.1002416463656472</v>
       </c>
       <c r="AC4">
-        <v>-0.4378966693647993</v>
+        <v>-0.4160167704438895</v>
       </c>
       <c r="AD4">
-        <v>179.2</v>
+        <v>160.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>179.2</v>
+        <v>160.6</v>
       </c>
       <c r="AG4">
-        <v>154</v>
+        <v>151.18</v>
       </c>
       <c r="AH4">
-        <v>0.6497461928934011</v>
+        <v>0.4949152542372881</v>
       </c>
       <c r="AI4">
-        <v>0.6111869031377899</v>
+        <v>0.9429309534992955</v>
       </c>
       <c r="AJ4">
-        <v>0.6145251396648045</v>
+        <v>0.4798146502475562</v>
       </c>
       <c r="AK4">
-        <v>0.5746268656716418</v>
+        <v>0.9395898073337476</v>
       </c>
       <c r="AL4">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="AM4">
-        <v>9.65</v>
+        <v>17.8</v>
       </c>
       <c r="AN4">
-        <v>-2.174757281553398</v>
+        <v>-16.7816091954023</v>
       </c>
       <c r="AO4">
-        <v>-6.481203007518797</v>
+        <v>-2.735955056179775</v>
       </c>
       <c r="AP4">
-        <v>-1.868932038834951</v>
+        <v>-15.79728317659352</v>
       </c>
       <c r="AQ4">
-        <v>-8.932642487046632</v>
+        <v>-2.735955056179775</v>
       </c>
     </row>
     <row r="5">
@@ -975,25 +978,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0775</v>
+        <v>0.0883</v>
       </c>
       <c r="G5">
-        <v>-0.02767797737857618</v>
+        <v>-0.02498498498498498</v>
       </c>
       <c r="H5">
-        <v>-0.02767797737857618</v>
+        <v>-0.02498498498498498</v>
       </c>
       <c r="I5">
-        <v>-0.2927478376580173</v>
+        <v>-0.2906906906906907</v>
       </c>
       <c r="J5">
-        <v>-0.2827553781326236</v>
+        <v>-0.2763401376059604</v>
       </c>
       <c r="K5">
-        <v>21.7</v>
+        <v>22.7</v>
       </c>
       <c r="L5">
-        <v>0.1443779108449767</v>
+        <v>0.1363363363363363</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1017,198 +1020,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>5.03</v>
+        <v>15.7</v>
       </c>
       <c r="V5">
-        <v>0.2372641509433963</v>
+        <v>0.5395189003436426</v>
       </c>
       <c r="W5">
-        <v>-0.0964015992892048</v>
+        <v>-0.09969257795344752</v>
       </c>
       <c r="X5">
-        <v>1.303175220460981</v>
+        <v>0.5748343177309201</v>
       </c>
       <c r="Y5">
-        <v>-1.399576819750186</v>
+        <v>-0.6745268956843676</v>
       </c>
       <c r="Z5">
-        <v>1.224938875305624</v>
+        <v>2.671265843093212</v>
       </c>
       <c r="AA5">
-        <v>-0.3463580548763923</v>
+        <v>-0.7381779706624798</v>
       </c>
       <c r="AB5">
-        <v>0.1448697447771639</v>
+        <v>0.1017473170150059</v>
       </c>
       <c r="AC5">
-        <v>-0.4912277996535562</v>
+        <v>-0.8399252876774856</v>
       </c>
       <c r="AD5">
-        <v>306.9</v>
+        <v>268.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>306.9</v>
+        <v>268.6</v>
       </c>
       <c r="AG5">
-        <v>301.87</v>
+        <v>252.9</v>
       </c>
       <c r="AH5">
-        <v>0.9353855531850046</v>
+        <v>0.9022505878401075</v>
       </c>
       <c r="AI5">
-        <v>1.613564668769716</v>
+        <v>1.94356005788712</v>
       </c>
       <c r="AJ5">
-        <v>0.9343795462283716</v>
+        <v>0.8968085106382978</v>
       </c>
       <c r="AK5">
-        <v>1.630231678997678</v>
+        <v>2.064489795918367</v>
       </c>
       <c r="AL5">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="AM5">
-        <v>19.73</v>
+        <v>19.22</v>
       </c>
       <c r="AN5">
-        <v>-73.77403846153845</v>
+        <v>-39.2116788321168</v>
       </c>
       <c r="AO5">
-        <v>-1.795918367346939</v>
+        <v>-2</v>
       </c>
       <c r="AP5">
-        <v>-72.56490384615384</v>
+        <v>-36.91970802919709</v>
       </c>
       <c r="AQ5">
-        <v>-2.230106436898124</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sporting Clube de Braga - Futebol, SAD (ENXTLS:SCB)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.09910000000000001</v>
-      </c>
-      <c r="E6">
-        <v>0.0229</v>
-      </c>
-      <c r="G6">
-        <v>-0.6929577464788733</v>
-      </c>
-      <c r="H6">
-        <v>-0.6929577464788733</v>
-      </c>
-      <c r="I6">
-        <v>-1.322904545496086</v>
-      </c>
-      <c r="J6">
-        <v>-1.282230166933072</v>
-      </c>
-      <c r="K6">
-        <v>3.25</v>
-      </c>
-      <c r="L6">
-        <v>0.2288732394366197</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0.1409890698513052</v>
-      </c>
-      <c r="Z6">
-        <v>85.42754640733195</v>
-      </c>
-      <c r="AA6">
-        <v>-109.537777090556</v>
-      </c>
-      <c r="AB6">
-        <v>0.1404979241427579</v>
-      </c>
-      <c r="AC6">
-        <v>-109.6782750146988</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0.1662227302220781</v>
-      </c>
-      <c r="AF6">
-        <v>0.1662227302220781</v>
-      </c>
-      <c r="AG6">
-        <v>0.1662227302220781</v>
-      </c>
-      <c r="AH6">
-        <v>0.006451187353399296</v>
-      </c>
-      <c r="AI6">
-        <v>1</v>
-      </c>
-      <c r="AJ6">
-        <v>0.006451187353399296</v>
-      </c>
-      <c r="AK6">
-        <v>1</v>
-      </c>
-      <c r="AL6">
-        <v>1.02</v>
-      </c>
-      <c r="AM6">
-        <v>0.647</v>
-      </c>
-      <c r="AN6">
-        <v>-0</v>
-      </c>
-      <c r="AO6">
-        <v>-18.43137254901961</v>
-      </c>
-      <c r="AP6">
-        <v>-0.01697536052104556</v>
-      </c>
-      <c r="AQ6">
-        <v>-29.05718701700155</v>
+        <v>-2.518210197710718</v>
       </c>
     </row>
   </sheetData>
